--- a/Result/profitability/5312.xlsx
+++ b/Result/profitability/5312.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.68</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5825</v>
+        <v>1.54375</v>
       </c>
       <c r="N2" t="n">
-        <v>63.3725</v>
+        <v>63.75</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3325</v>
+        <v>1.40625</v>
       </c>
       <c r="N3" t="n">
-        <v>63.6275</v>
+        <v>63.62875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.83</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2375</v>
+        <v>1.26</v>
       </c>
       <c r="N4" t="n">
-        <v>63.13</v>
+        <v>63.4125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03875</v>
+        <v>1.21625</v>
       </c>
       <c r="N5" t="n">
-        <v>63.09125</v>
+        <v>63.16625000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.045</v>
+        <v>0.9925</v>
       </c>
       <c r="N6" t="n">
-        <v>62.695</v>
+        <v>62.8575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.51</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7837499999999999</v>
+        <v>0.9237500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>62.355</v>
+        <v>62.65000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7487499999999999</v>
+        <v>0.83625</v>
       </c>
       <c r="N8" t="n">
-        <v>61.765</v>
+        <v>61.9225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.55</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.6325</v>
       </c>
       <c r="N9" t="n">
         <v>62.32875</v>
@@ -1772,7 +1772,7 @@
         <v>0.91</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7175</v>
+        <v>0.7174999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>61.485</v>
@@ -1899,7 +1899,7 @@
         <v>1.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7424999999999999</v>
+        <v>0.7425</v>
       </c>
       <c r="N12" t="n">
         <v>61.34375</v>
@@ -2026,7 +2026,7 @@
         <v>0.95</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8099999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>61.47500000000001</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1098</v>
+      </c>
+      <c r="D75" t="n">
+        <v>383</v>
+      </c>
+      <c r="E75" t="n">
+        <v>715</v>
+      </c>
+      <c r="F75" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>69</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.29%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>83</v>
+      </c>
+      <c r="J75" t="n">
+        <v>152</v>
+      </c>
+      <c r="K75" t="n">
+        <v>131</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N75" t="n">
+        <v>63.75875000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.472972972972973</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.259999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01973375097885666</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.868421052631579</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5999999999999943</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.009300883583940323</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
